--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T09:24:58+00:00</t>
+    <t>2025-02-07T10:03:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:03:43+00:00</t>
+    <t>2025-02-07T10:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5568" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5568" uniqueCount="610">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T11:56:07+00:00</t>
+    <t>2025-03-08T15:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1443,9 +1443,6 @@
   </si>
   <si>
     <t>Appointment.participant:HL7ATCorePatient.actor.display</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
   </si>
   <si>
     <t>Appointment.participant:HL7ATCorePatient.required</t>
@@ -9163,13 +9160,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -9869,7 +9866,7 @@
         <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>18</v>
@@ -9887,7 +9884,7 @@
         <v>417</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>449</v>
+        <v>202</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9969,7 +9966,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>419</v>
@@ -10086,7 +10083,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>426</v>
@@ -10103,7 +10100,7 @@
         <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -10201,13 +10198,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>347</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>18</v>
@@ -10318,7 +10315,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>358</v>
@@ -10433,7 +10430,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>363</v>
@@ -10550,7 +10547,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>366</v>
@@ -10669,7 +10666,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>371</v>
@@ -10786,7 +10783,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>380</v>
@@ -10901,7 +10898,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>383</v>
@@ -10912,13 +10909,13 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>18</v>
@@ -10927,7 +10924,7 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>385</v>
@@ -11018,7 +11015,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>391</v>
@@ -11133,7 +11130,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>392</v>
@@ -11250,7 +11247,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>395</v>
@@ -11367,7 +11364,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>401</v>
@@ -11484,7 +11481,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>408</v>
@@ -11601,7 +11598,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>415</v>
@@ -11618,7 +11615,7 @@
         <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>18</v>
@@ -11636,7 +11633,7 @@
         <v>417</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>449</v>
+        <v>202</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11718,7 +11715,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>419</v>
@@ -11835,7 +11832,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>426</v>
@@ -11852,7 +11849,7 @@
         <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>18</v>
@@ -11950,13 +11947,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>347</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>18</v>
@@ -12067,7 +12064,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>358</v>
@@ -12182,7 +12179,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>363</v>
@@ -12299,7 +12296,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>366</v>
@@ -12418,7 +12415,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>371</v>
@@ -12535,7 +12532,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>380</v>
@@ -12650,7 +12647,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>383</v>
@@ -12661,13 +12658,13 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>18</v>
@@ -12676,7 +12673,7 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>385</v>
@@ -12767,7 +12764,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>391</v>
@@ -12882,7 +12879,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>392</v>
@@ -12999,7 +12996,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>395</v>
@@ -13116,7 +13113,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>401</v>
@@ -13233,7 +13230,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>408</v>
@@ -13350,7 +13347,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>415</v>
@@ -13367,7 +13364,7 @@
         <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>18</v>
@@ -13385,7 +13382,7 @@
         <v>417</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>449</v>
+        <v>202</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13467,7 +13464,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>419</v>
@@ -13584,7 +13581,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>426</v>
@@ -13601,7 +13598,7 @@
         <v>87</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>18</v>
@@ -13699,13 +13696,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>347</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>18</v>
@@ -13816,7 +13813,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>358</v>
@@ -13931,7 +13928,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>363</v>
@@ -14048,7 +14045,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>366</v>
@@ -14167,7 +14164,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>371</v>
@@ -14284,7 +14281,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>380</v>
@@ -14399,7 +14396,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>383</v>
@@ -14410,13 +14407,13 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>18</v>
@@ -14425,7 +14422,7 @@
         <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>385</v>
@@ -14516,7 +14513,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>391</v>
@@ -14631,7 +14628,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>392</v>
@@ -14748,7 +14745,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>395</v>
@@ -14865,7 +14862,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>401</v>
@@ -14982,7 +14979,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>408</v>
@@ -15099,7 +15096,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>415</v>
@@ -15116,7 +15113,7 @@
         <v>87</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>18</v>
@@ -15134,7 +15131,7 @@
         <v>417</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>449</v>
+        <v>202</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15216,7 +15213,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>419</v>
@@ -15333,7 +15330,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>426</v>
@@ -15350,7 +15347,7 @@
         <v>87</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>18</v>
@@ -15448,10 +15445,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15477,10 +15474,10 @@
         <v>284</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15531,7 +15528,7 @@
         <v>18</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15563,10 +15560,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15592,13 +15589,13 @@
         <v>420</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15648,7 +15645,7 @@
         <v>18</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15680,10 +15677,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15709,10 +15706,10 @@
         <v>348</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15763,7 +15760,7 @@
         <v>18</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15795,10 +15792,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15910,10 +15907,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16027,10 +16024,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16146,10 +16143,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16175,10 +16172,10 @@
         <v>168</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16208,11 +16205,11 @@
         <v>111</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="Z120" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AA120" t="s" s="2">
         <v>18</v>
       </c>
@@ -16229,7 +16226,7 @@
         <v>18</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16253,7 +16250,7 @@
         <v>132</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>18</v>
@@ -16261,10 +16258,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16290,10 +16287,10 @@
         <v>168</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16323,10 +16320,10 @@
         <v>178</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>18</v>
@@ -16344,7 +16341,7 @@
         <v>18</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>87</v>
@@ -16368,7 +16365,7 @@
         <v>18</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>18</v>
@@ -16376,10 +16373,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16402,13 +16399,13 @@
         <v>18</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16459,7 +16456,7 @@
         <v>18</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16483,7 +16480,7 @@
         <v>18</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>18</v>
@@ -16491,10 +16488,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16520,10 +16517,10 @@
         <v>284</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16574,7 +16571,7 @@
         <v>18</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16598,7 +16595,7 @@
         <v>18</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>18</v>
@@ -16606,10 +16603,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16632,13 +16629,13 @@
         <v>18</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16689,7 +16686,7 @@
         <v>18</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16713,7 +16710,7 @@
         <v>18</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>18</v>
@@ -16721,10 +16718,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16750,10 +16747,10 @@
         <v>348</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16804,7 +16801,7 @@
         <v>18</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16836,10 +16833,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16951,10 +16948,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17068,10 +17065,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17187,10 +17184,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17216,10 +17213,10 @@
         <v>420</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17270,7 +17267,7 @@
         <v>18</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17302,10 +17299,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17331,10 +17328,10 @@
         <v>420</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17385,7 +17382,7 @@
         <v>18</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17417,10 +17414,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17446,10 +17443,10 @@
         <v>420</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17500,7 +17497,7 @@
         <v>18</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17532,10 +17529,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17561,10 +17558,10 @@
         <v>420</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17615,7 +17612,7 @@
         <v>18</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17647,10 +17644,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17676,10 +17673,10 @@
         <v>420</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17730,7 +17727,7 @@
         <v>18</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17762,10 +17759,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17791,10 +17788,10 @@
         <v>420</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17845,7 +17842,7 @@
         <v>18</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17877,10 +17874,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17906,10 +17903,10 @@
         <v>420</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17960,7 +17957,7 @@
         <v>18</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17992,10 +17989,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18021,10 +18018,10 @@
         <v>284</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18075,7 +18072,7 @@
         <v>18</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -18107,10 +18104,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18136,10 +18133,10 @@
         <v>348</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -18190,7 +18187,7 @@
         <v>18</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18222,10 +18219,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18337,10 +18334,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18454,10 +18451,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18573,10 +18570,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18602,10 +18599,10 @@
         <v>284</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18656,7 +18653,7 @@
         <v>18</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18688,10 +18685,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18714,13 +18711,13 @@
         <v>18</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18750,11 +18747,11 @@
         <v>111</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="Z142" t="s" s="2">
-        <v>584</v>
-      </c>
       <c r="AA142" t="s" s="2">
         <v>18</v>
       </c>
@@ -18771,7 +18768,7 @@
         <v>18</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18803,10 +18800,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18829,16 +18826,16 @@
         <v>18</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18867,11 +18864,11 @@
         <v>111</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="Z143" t="s" s="2">
-        <v>590</v>
-      </c>
       <c r="AA143" t="s" s="2">
         <v>18</v>
       </c>
@@ -18888,7 +18885,7 @@
         <v>18</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -18920,10 +18917,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18949,10 +18946,10 @@
         <v>284</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19003,7 +19000,7 @@
         <v>18</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>87</v>
@@ -19035,10 +19032,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19064,10 +19061,10 @@
         <v>348</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19118,7 +19115,7 @@
         <v>18</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -19150,10 +19147,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19265,10 +19262,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19382,10 +19379,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19501,10 +19498,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19530,10 +19527,10 @@
         <v>284</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19584,7 +19581,7 @@
         <v>18</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>87</v>
@@ -19616,10 +19613,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19642,16 +19639,16 @@
         <v>18</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19701,7 +19698,7 @@
         <v>18</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19725,7 +19722,7 @@
         <v>18</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>18</v>
@@ -19733,10 +19730,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19762,13 +19759,13 @@
         <v>284</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19818,7 +19815,7 @@
         <v>18</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T15:01:54+00:00</t>
+    <t>2025-03-08T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T16:16:40+00:00</t>
+    <t>2025-03-12T07:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T07:45:08+00:00</t>
+    <t>2025-03-21T10:14:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T13:03:45+00:00</t>
+    <t>2026-01-12T10:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:18:34+00:00</t>
+    <t>2026-01-12T10:26:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:26:55+00:00</t>
+    <t>2026-01-28T07:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:37:37+00:00</t>
+    <t>2026-01-28T07:43:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:43:18+00:00</t>
+    <t>2026-01-28T07:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:44:30+00:00</t>
+    <t>2026-01-28T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:46:49+00:00</t>
+    <t>2026-02-24T18:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T18:21:42+00:00</t>
+    <t>2026-02-26T08:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:55:53+00:00</t>
+    <t>2026-03-06T07:38:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T07:38:40+00:00</t>
+    <t>2026-03-06T14:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T09:58:26+00:00</t>
+    <t>2026-03-11T09:54:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5964" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5963" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T09:54:15+00:00</t>
+    <t>2026-03-18T07:58:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -700,13 +700,10 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>Classification of the encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/EncounterClass</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/encounter-class</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -752,9 +749,6 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
@@ -774,6 +768,9 @@
   </si>
   <si>
     <t>ToDo</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|5.0.0</t>
@@ -4687,11 +4684,9 @@
       <c r="X20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Y20" s="2"/>
+      <c r="Z20" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4727,24 +4722,24 @@
         <v>18</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4770,10 +4765,10 @@
         <v>175</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4804,7 +4799,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>18</v>
@@ -4822,7 +4817,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4843,10 +4838,10 @@
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>18</v>
@@ -4854,10 +4849,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4880,16 +4875,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4915,11 +4910,11 @@
         <v>18</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>18</v>
@@ -4937,7 +4932,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4952,27 +4947,27 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4998,13 +4993,13 @@
         <v>175</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5030,11 +5025,11 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -5052,7 +5047,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -5070,10 +5065,10 @@
         <v>18</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>18</v>
@@ -5084,10 +5079,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5113,10 +5108,10 @@
         <v>175</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5143,11 +5138,11 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -5165,7 +5160,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -5186,21 +5181,21 @@
         <v>18</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5223,13 +5218,13 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5256,14 +5251,14 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
       </c>
@@ -5280,7 +5275,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5295,27 +5290,27 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5341,13 +5336,13 @@
         <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5376,11 +5371,11 @@
         <v>178</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
@@ -5397,7 +5392,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5412,27 +5407,27 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5458,10 +5453,10 @@
         <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5512,7 +5507,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -5533,21 +5528,21 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>276</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5570,13 +5565,13 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5627,7 +5622,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5642,16 +5637,16 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>18</v>
@@ -5659,10 +5654,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5685,16 +5680,16 @@
         <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5744,7 +5739,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5776,10 +5771,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5802,13 +5797,13 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5859,7 +5854,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5874,16 +5869,16 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
@@ -5891,10 +5886,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5917,16 +5912,16 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5976,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5994,7 +5989,7 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>132</v>
@@ -6008,10 +6003,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6034,16 +6029,16 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6093,7 +6088,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -6102,7 +6097,7 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
@@ -6111,7 +6106,7 @@
         <v>18</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>132</v>
@@ -6125,10 +6120,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6151,16 +6146,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6210,7 +6205,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6219,33 +6214,33 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6268,16 +6263,16 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>317</v>
-      </c>
       <c r="N34" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6327,7 +6322,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6336,33 +6331,33 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6385,13 +6380,13 @@
         <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6442,7 +6437,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6457,16 +6452,16 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>18</v>
@@ -6474,10 +6469,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6500,16 +6495,16 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6559,7 +6554,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6574,27 +6569,27 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6617,13 +6612,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6674,7 +6669,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6695,7 +6690,7 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>18</v>
@@ -6706,10 +6701,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6732,16 +6727,16 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6791,7 +6786,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6812,7 +6807,7 @@
         <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>18</v>
@@ -6823,10 +6818,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6849,16 +6844,16 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6908,7 +6903,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6923,16 +6918,16 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6940,10 +6935,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6966,16 +6961,16 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7025,7 +7020,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -7034,7 +7029,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -7057,10 +7052,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7083,16 +7078,16 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7142,7 +7137,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7157,27 +7152,27 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="AO41" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7200,13 +7195,13 @@
         <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7257,7 +7252,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7278,25 +7273,25 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7315,13 +7310,13 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7372,7 +7367,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7387,13 +7382,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
@@ -7404,10 +7399,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7430,13 +7425,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7487,7 +7482,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7505,24 +7500,24 @@
         <v>18</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7545,16 +7540,16 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="N45" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7592,7 +7587,7 @@
         <v>18</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -7602,7 +7597,7 @@
         <v>138</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7614,30 +7609,30 @@
         <v>18</v>
       </c>
       <c r="AJ45" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AK45" t="s" s="2">
+      <c r="AL45" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7749,10 +7744,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7862,13 +7857,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>18</v>
@@ -7890,13 +7885,13 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7979,14 +7974,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8008,10 +8003,10 @@
         <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>150</v>
@@ -8066,7 +8061,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8098,10 +8093,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8127,13 +8122,13 @@
         <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8159,14 +8154,14 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8183,7 +8178,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8192,7 +8187,7 @@
         <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -8204,21 +8199,21 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>181</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8241,13 +8236,13 @@
         <v>18</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8298,7 +8293,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8330,10 +8325,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8356,16 +8351,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8415,7 +8410,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8424,7 +8419,7 @@
         <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>99</v>
@@ -8433,24 +8428,24 @@
         <v>18</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8562,10 +8557,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8679,10 +8674,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8708,13 +8703,13 @@
         <v>207</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8764,16 +8759,16 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>99</v>
@@ -8796,10 +8791,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8825,13 +8820,13 @@
         <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8857,31 +8852,31 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z56" t="s" s="2">
+      <c r="AA56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8913,10 +8908,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8942,13 +8937,13 @@
         <v>154</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8998,16 +8993,16 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI57" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>99</v>
@@ -9019,7 +9014,7 @@
         <v>18</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>18</v>
@@ -9030,10 +9025,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9059,13 +9054,13 @@
         <v>207</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N58" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9115,7 +9110,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -9124,7 +9119,7 @@
         <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>99</v>
@@ -9147,10 +9142,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9173,16 +9168,16 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9232,7 +9227,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9253,10 +9248,10 @@
         <v>18</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9264,10 +9259,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9293,10 +9288,10 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9326,11 +9321,11 @@
         <v>111</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9347,7 +9342,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>87</v>
@@ -9368,24 +9363,24 @@
         <v>18</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>18</v>
@@ -9407,13 +9402,13 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9464,7 +9459,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>87</v>
@@ -9476,30 +9471,30 @@
         <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9611,10 +9606,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9724,13 +9719,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>18</v>
@@ -9752,13 +9747,13 @@
         <v>18</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9841,14 +9836,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9870,10 +9865,10 @@
         <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>150</v>
@@ -9928,7 +9923,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9960,10 +9955,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9989,13 +9984,13 @@
         <v>175</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10021,14 +10016,14 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
       </c>
@@ -10045,7 +10040,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10054,7 +10049,7 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
@@ -10066,21 +10061,21 @@
         <v>18</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>181</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10103,13 +10098,13 @@
         <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10160,7 +10155,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10192,10 +10187,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10218,16 +10213,16 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10277,7 +10272,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10286,7 +10281,7 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>99</v>
@@ -10295,24 +10290,24 @@
         <v>18</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10424,10 +10419,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10541,10 +10536,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10570,13 +10565,13 @@
         <v>207</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10626,16 +10621,16 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>99</v>
@@ -10658,10 +10653,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10687,13 +10682,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10719,31 +10714,31 @@
         <v>18</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z72" t="s" s="2">
+      <c r="AA72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10775,10 +10770,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10804,13 +10799,13 @@
         <v>154</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10860,16 +10855,16 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>99</v>
@@ -10881,7 +10876,7 @@
         <v>18</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>18</v>
@@ -10892,10 +10887,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10921,13 +10916,13 @@
         <v>207</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N74" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10977,7 +10972,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10986,7 +10981,7 @@
         <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>99</v>
@@ -11009,10 +11004,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11035,16 +11030,16 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11094,7 +11089,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11115,10 +11110,10 @@
         <v>18</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>18</v>
@@ -11126,10 +11121,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11155,10 +11150,10 @@
         <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11188,11 +11183,11 @@
         <v>111</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>18</v>
       </c>
@@ -11209,7 +11204,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -11230,24 +11225,24 @@
         <v>18</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>18</v>
@@ -11269,13 +11264,13 @@
         <v>18</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11326,7 +11321,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>87</v>
@@ -11338,30 +11333,30 @@
         <v>18</v>
       </c>
       <c r="AJ77" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AK77" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AK77" t="s" s="2">
+      <c r="AL77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL77" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11473,10 +11468,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11586,13 +11581,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>18</v>
@@ -11614,13 +11609,13 @@
         <v>18</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11703,14 +11698,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11732,10 +11727,10 @@
         <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>150</v>
@@ -11790,7 +11785,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11822,10 +11817,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11851,13 +11846,13 @@
         <v>175</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11883,14 +11878,14 @@
         <v>18</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>18</v>
       </c>
@@ -11907,7 +11902,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11916,7 +11911,7 @@
         <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>99</v>
@@ -11928,21 +11923,21 @@
         <v>18</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>181</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11965,13 +11960,13 @@
         <v>18</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12022,7 +12017,7 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12054,10 +12049,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12080,16 +12075,16 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12139,7 +12134,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12148,7 +12143,7 @@
         <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>99</v>
@@ -12157,24 +12152,24 @@
         <v>18</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12286,10 +12281,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12403,10 +12398,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12432,13 +12427,13 @@
         <v>207</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12488,16 +12483,16 @@
         <v>18</v>
       </c>
       <c r="AF87" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>99</v>
@@ -12520,10 +12515,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12549,13 +12544,13 @@
         <v>101</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12581,31 +12576,31 @@
         <v>18</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12637,10 +12632,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12666,13 +12661,13 @@
         <v>154</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12722,16 +12717,16 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>99</v>
@@ -12743,7 +12738,7 @@
         <v>18</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>18</v>
@@ -12754,10 +12749,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12783,13 +12778,13 @@
         <v>207</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N90" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12839,7 +12834,7 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12848,7 +12843,7 @@
         <v>87</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>99</v>
@@ -12871,10 +12866,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12897,16 +12892,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12956,7 +12951,7 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12977,10 +12972,10 @@
         <v>18</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>18</v>
@@ -12988,10 +12983,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13017,10 +13012,10 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13050,11 +13045,11 @@
         <v>111</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>18</v>
       </c>
@@ -13071,7 +13066,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>87</v>
@@ -13092,24 +13087,24 @@
         <v>18</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>18</v>
@@ -13131,13 +13126,13 @@
         <v>18</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13188,7 +13183,7 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>87</v>
@@ -13200,30 +13195,30 @@
         <v>18</v>
       </c>
       <c r="AJ93" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AK93" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AK93" t="s" s="2">
+      <c r="AL93" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL93" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13335,10 +13330,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13448,13 +13443,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>18</v>
@@ -13476,13 +13471,13 @@
         <v>18</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13565,14 +13560,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13594,10 +13589,10 @@
         <v>134</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>150</v>
@@ -13652,7 +13647,7 @@
         <v>18</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13684,10 +13679,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13713,13 +13708,13 @@
         <v>175</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13745,14 +13740,14 @@
         <v>18</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Z98" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>18</v>
       </c>
@@ -13769,7 +13764,7 @@
         <v>18</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13778,7 +13773,7 @@
         <v>77</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>99</v>
@@ -13790,21 +13785,21 @@
         <v>18</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>181</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13827,13 +13822,13 @@
         <v>18</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13884,7 +13879,7 @@
         <v>18</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13916,10 +13911,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13942,16 +13937,16 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14001,7 +13996,7 @@
         <v>18</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -14010,7 +14005,7 @@
         <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>99</v>
@@ -14019,24 +14014,24 @@
         <v>18</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN100" t="s" s="2">
+      <c r="AO100" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14148,10 +14143,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14265,10 +14260,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14294,13 +14289,13 @@
         <v>207</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14350,16 +14345,16 @@
         <v>18</v>
       </c>
       <c r="AF103" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -14382,10 +14377,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14411,13 +14406,13 @@
         <v>101</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14443,31 +14438,31 @@
         <v>18</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z104" t="s" s="2">
+      <c r="AA104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14499,10 +14494,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14528,13 +14523,13 @@
         <v>154</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14584,16 +14579,16 @@
         <v>18</v>
       </c>
       <c r="AF105" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI105" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>99</v>
@@ -14605,7 +14600,7 @@
         <v>18</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>18</v>
@@ -14616,10 +14611,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14645,13 +14640,13 @@
         <v>207</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M106" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N106" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14701,7 +14696,7 @@
         <v>18</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14710,7 +14705,7 @@
         <v>87</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>99</v>
@@ -14733,10 +14728,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14759,16 +14754,16 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14818,7 +14813,7 @@
         <v>18</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14839,10 +14834,10 @@
         <v>18</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>18</v>
@@ -14850,10 +14845,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14879,10 +14874,10 @@
         <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14912,11 +14907,11 @@
         <v>111</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z108" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z108" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA108" t="s" s="2">
         <v>18</v>
       </c>
@@ -14933,7 +14928,7 @@
         <v>18</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -14954,24 +14949,24 @@
         <v>18</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>18</v>
@@ -14993,13 +14988,13 @@
         <v>18</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15050,7 +15045,7 @@
         <v>18</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>87</v>
@@ -15062,30 +15057,30 @@
         <v>18</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AK109" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AK109" t="s" s="2">
+      <c r="AL109" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL109" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM109" t="s" s="2">
+      <c r="AN109" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN109" t="s" s="2">
+      <c r="AO109" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15197,10 +15192,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15310,13 +15305,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>18</v>
@@ -15338,13 +15333,13 @@
         <v>18</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15427,14 +15422,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15456,10 +15451,10 @@
         <v>134</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>150</v>
@@ -15514,7 +15509,7 @@
         <v>18</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15546,10 +15541,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15575,13 +15570,13 @@
         <v>175</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15607,14 +15602,14 @@
         <v>18</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Z114" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>18</v>
       </c>
@@ -15631,7 +15626,7 @@
         <v>18</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15640,7 +15635,7 @@
         <v>77</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>99</v>
@@ -15652,21 +15647,21 @@
         <v>18</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>181</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15689,13 +15684,13 @@
         <v>18</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15746,7 +15741,7 @@
         <v>18</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15778,10 +15773,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15804,16 +15799,16 @@
         <v>88</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15863,7 +15858,7 @@
         <v>18</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15872,7 +15867,7 @@
         <v>87</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>99</v>
@@ -15881,24 +15876,24 @@
         <v>18</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AN116" t="s" s="2">
+      <c r="AO116" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16010,10 +16005,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16127,10 +16122,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16156,13 +16151,13 @@
         <v>207</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16212,16 +16207,16 @@
         <v>18</v>
       </c>
       <c r="AF119" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI119" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>99</v>
@@ -16244,10 +16239,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16273,13 +16268,13 @@
         <v>101</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16305,31 +16300,31 @@
         <v>18</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z120" t="s" s="2">
+      <c r="AA120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16361,10 +16356,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16390,13 +16385,13 @@
         <v>154</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16446,16 +16441,16 @@
         <v>18</v>
       </c>
       <c r="AF121" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI121" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>99</v>
@@ -16467,7 +16462,7 @@
         <v>18</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>18</v>
@@ -16478,10 +16473,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16507,13 +16502,13 @@
         <v>207</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M122" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N122" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16563,7 +16558,7 @@
         <v>18</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16572,7 +16567,7 @@
         <v>87</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>99</v>
@@ -16595,10 +16590,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16621,16 +16616,16 @@
         <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16680,7 +16675,7 @@
         <v>18</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16701,10 +16696,10 @@
         <v>18</v>
       </c>
       <c r="AM123" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>18</v>
@@ -16712,10 +16707,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16741,10 +16736,10 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16774,11 +16769,11 @@
         <v>111</v>
       </c>
       <c r="Y124" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z124" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z124" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA124" t="s" s="2">
         <v>18</v>
       </c>
@@ -16795,7 +16790,7 @@
         <v>18</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>87</v>
@@ -16816,21 +16811,21 @@
         <v>18</v>
       </c>
       <c r="AM124" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN124" t="s" s="2">
+      <c r="AO124" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16853,13 +16848,13 @@
         <v>18</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16910,7 +16905,7 @@
         <v>18</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16942,10 +16937,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16968,16 +16963,16 @@
         <v>18</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17027,7 +17022,7 @@
         <v>18</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -17059,10 +17054,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17085,13 +17080,13 @@
         <v>18</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17142,7 +17137,7 @@
         <v>18</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -17151,7 +17146,7 @@
         <v>77</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>99</v>
@@ -17174,10 +17169,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17289,10 +17284,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17406,14 +17401,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17435,10 +17430,10 @@
         <v>134</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>150</v>
@@ -17493,7 +17488,7 @@
         <v>18</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17525,10 +17520,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17554,10 +17549,10 @@
         <v>175</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17587,11 +17582,11 @@
         <v>111</v>
       </c>
       <c r="Y131" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="Z131" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="Z131" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="AA131" t="s" s="2">
         <v>18</v>
       </c>
@@ -17608,7 +17603,7 @@
         <v>18</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17632,7 +17627,7 @@
         <v>132</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>18</v>
@@ -17640,10 +17635,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17669,10 +17664,10 @@
         <v>175</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17699,13 +17694,13 @@
         <v>18</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>18</v>
@@ -17723,7 +17718,7 @@
         <v>18</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>87</v>
@@ -17747,7 +17742,7 @@
         <v>18</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>18</v>
@@ -17755,10 +17750,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17781,13 +17776,13 @@
         <v>18</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17838,7 +17833,7 @@
         <v>18</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17862,7 +17857,7 @@
         <v>18</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>18</v>
@@ -17870,10 +17865,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17896,13 +17891,13 @@
         <v>18</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17953,7 +17948,7 @@
         <v>18</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17977,7 +17972,7 @@
         <v>18</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>18</v>
@@ -17985,10 +17980,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18011,13 +18006,13 @@
         <v>18</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18068,7 +18063,7 @@
         <v>18</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -18092,7 +18087,7 @@
         <v>18</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>18</v>
@@ -18100,10 +18095,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18126,13 +18121,13 @@
         <v>18</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18183,7 +18178,7 @@
         <v>18</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -18215,10 +18210,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18330,10 +18325,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18447,14 +18442,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -18476,10 +18471,10 @@
         <v>134</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>150</v>
@@ -18534,7 +18529,7 @@
         <v>18</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -18566,10 +18561,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18592,13 +18587,13 @@
         <v>18</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18649,7 +18644,7 @@
         <v>18</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18681,10 +18676,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18707,13 +18702,13 @@
         <v>18</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18764,7 +18759,7 @@
         <v>18</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18796,10 +18791,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18822,13 +18817,13 @@
         <v>18</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18879,7 +18874,7 @@
         <v>18</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18911,10 +18906,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18937,13 +18932,13 @@
         <v>18</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18994,7 +18989,7 @@
         <v>18</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -19026,10 +19021,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19052,13 +19047,13 @@
         <v>18</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19109,7 +19104,7 @@
         <v>18</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -19141,10 +19136,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19167,13 +19162,13 @@
         <v>18</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19224,7 +19219,7 @@
         <v>18</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -19256,10 +19251,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19282,13 +19277,13 @@
         <v>18</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -19339,7 +19334,7 @@
         <v>18</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -19371,10 +19366,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19397,13 +19392,13 @@
         <v>18</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19454,7 +19449,7 @@
         <v>18</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19486,10 +19481,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19512,13 +19507,13 @@
         <v>18</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19569,7 +19564,7 @@
         <v>18</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19601,10 +19596,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19716,10 +19711,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19833,14 +19828,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19862,10 +19857,10 @@
         <v>134</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>150</v>
@@ -19920,7 +19915,7 @@
         <v>18</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19952,10 +19947,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19978,13 +19973,13 @@
         <v>18</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20035,7 +20030,7 @@
         <v>18</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
@@ -20067,10 +20062,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20096,10 +20091,10 @@
         <v>198</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -20129,11 +20124,11 @@
         <v>111</v>
       </c>
       <c r="Y153" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="Z153" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="Z153" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="AA153" t="s" s="2">
         <v>18</v>
       </c>
@@ -20150,7 +20145,7 @@
         <v>18</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -20182,10 +20177,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20211,13 +20206,13 @@
         <v>198</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -20246,11 +20241,11 @@
         <v>111</v>
       </c>
       <c r="Y154" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="Z154" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="Z154" t="s" s="2">
-        <v>627</v>
-      </c>
       <c r="AA154" t="s" s="2">
         <v>18</v>
       </c>
@@ -20267,7 +20262,7 @@
         <v>18</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -20299,10 +20294,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20325,13 +20320,13 @@
         <v>18</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20382,7 +20377,7 @@
         <v>18</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>87</v>
@@ -20414,10 +20409,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20440,13 +20435,13 @@
         <v>18</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -20497,7 +20492,7 @@
         <v>18</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -20529,10 +20524,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20644,10 +20639,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20761,14 +20756,14 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -20790,10 +20785,10 @@
         <v>134</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N159" t="s" s="2">
         <v>150</v>
@@ -20848,7 +20843,7 @@
         <v>18</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20880,10 +20875,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20906,13 +20901,13 @@
         <v>18</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -20963,7 +20958,7 @@
         <v>18</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>87</v>
@@ -20995,10 +20990,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21021,16 +21016,16 @@
         <v>18</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21080,7 +21075,7 @@
         <v>18</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -21104,7 +21099,7 @@
         <v>18</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>18</v>
@@ -21112,10 +21107,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21138,16 +21133,16 @@
         <v>18</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N162" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21197,7 +21192,7 @@
         <v>18</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T07:58:35+00:00</t>
+    <t>2026-04-07T11:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:55:37+00:00</t>
+    <t>2026-04-08T07:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T07:58:25+00:00</t>
+    <t>2026-06-09T13:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:05:25+00:00</t>
+    <t>2026-06-09T13:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:21+00:00</t>
+    <t>2026-06-09T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T19:55:01+00:00</t>
+    <t>2026-06-10T09:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-appointment</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-appointment</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:07:46+00:00</t>
+    <t>2026-08-18T08:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -463,7 +463,7 @@
     <t>postponementReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/appointment-postponementReason}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/appointment-postponementReason}
 </t>
   </si>
   <si>
@@ -625,7 +625,7 @@
     <t>cancellationPolicy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-ext-cancellationPolicy}
 </t>
   </si>
   <si>
@@ -736,7 +736,7 @@
     <t>Appointment.serviceType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-healthcareservice)
+    <t xml:space="preserve">CodeableReference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-healthcareservice)
 </t>
   </si>
   <si>
@@ -749,7 +749,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -881,7 +881,7 @@
     <t>Appointment.replaces</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-appointment)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-appointment)
 </t>
   </si>
   <si>
@@ -1073,7 +1073,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/at-scheduling-slot)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/at-scheduling-slot)
 </t>
   </si>
   <si>
@@ -1281,7 +1281,7 @@
     <t>virtualService</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/StructureDefinition/virtual-service-detail}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/tc/wg/scheduling/r5/StructureDefinition/virtual-service-detail}
 </t>
   </si>
   <si>
@@ -2383,7 +2383,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.6953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:43:24+00:00</t>
+    <t>2026-08-18T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:20:27+00:00</t>
+    <t>2026-08-31T14:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/StructureDefinition-at-scheduling-appointment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:45:12+00:00</t>
+    <t>2026-09-01T07:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
